--- a/recording_consent_forms/023_media_upload_for_synchronization--recording_consent_forms.xlsx
+++ b/recording_consent_forms/023_media_upload_for_synchronization--recording_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sync_permissions_options</t>
+          <t>sync_permissions_options_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sync-permissions-options</t>
+          <t>Sync Permissions Options 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sync_permissions_options</t>
+          <t>sync_permissions_options_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sync-permissions-options</t>
+          <t>Sync Permissions Options 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sync_permissions_options</t>
+          <t>sync_permissions_options_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sync-permissions-options</t>
+          <t>Sync Permissions Options 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -756,7 +756,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -849,7 +849,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sync_permissions_options_choices</t>
+          <t>sync_permissions_options_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sync_permissions_options_choices</t>
+          <t>sync_permissions_options_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sync_permissions_options_choices</t>
+          <t>sync_permissions_options_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sync_permissions_options_choices</t>
+          <t>sync_permissions_options_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sync_permissions_options_choices</t>
+          <t>sync_permissions_options_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sync_permissions_options_choices</t>
+          <t>sync_permissions_options_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
